--- a/ProjectDescription/MainActivity_FunctionNameReg.xlsx
+++ b/ProjectDescription/MainActivity_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1318,6 +1318,439 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>pollInitCheckResult</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>轮询等待初始化检查结果，就绪后展示自动隐藏对话框</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;pollInitCheckResult:155]</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时47分55秒</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>500ms 轮询间隔，最多等待 15 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>showInitCheckDialog</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>result&lt;InitCheckResult&gt;</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>展示初始化检查结果的自动隐藏模态对话框，3 秒后自动关闭</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;showInitCheckDialog:186]</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时47分55秒</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>使用 AlertDialog + 自定义布局</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>应用主Activity，管理底部导航栏和Fragment切换</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity:26]</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>继承AppCompatActivity，3个Tab页面的容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>onCreate</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Activity创建回调，初始化界面、边缘显示、底部导航和Fragment</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;onCreate:43]</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>设置EdgeToEdge，绑定底部导航选择监听器</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>switchFragment</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>fragmentClass&lt;Class&lt;T&gt;&gt;, fragmentRef&lt;Fragment&gt;, tag&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>通用Fragment切换方法，懒加载创建，隐藏/显示切换</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;switchFragment:122]</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>使用hide/show替代replace，避免重复创建Fragment实例</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>应用主Activity，管理底部导航栏和Fragment切换</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity:26]</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>继承AppCompatActivity，3个Tab页面的容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>onCreate</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Activity创建回调，初始化界面、边缘显示、底部导航和Fragment</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;onCreate:43]</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>设置EdgeToEdge，绑定底部导航选择监听器</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>switchFragment</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>fragmentClass&lt;Class&lt;T&gt;&gt;, fragmentRef&lt;Fragment&gt;, tag&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>通用Fragment切换方法，懒加载创建，隐藏/显示切换</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;switchFragment:122]</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>使用hide/show替代replace，避免重复创建Fragment实例</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>应用主Activity，管理底部导航栏和Fragment切换</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity:26]</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>继承AppCompatActivity，3个Tab页面的容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>onCreate</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Activity创建回调，初始化界面、边缘显示、底部导航和Fragment</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;onCreate:43]</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>设置EdgeToEdge，绑定底部导航选择监听器</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>switchFragment</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>fragmentClass&lt;Class&lt;T&gt;&gt;, fragmentRef&lt;Fragment&gt;, tag&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>通用Fragment切换方法，懒加载创建，隐藏/显示切换</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;switchFragment:122]</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>使用hide/show替代replace，避免重复创建Fragment实例</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/MainActivity_FunctionNameReg.xlsx
+++ b/ProjectDescription/MainActivity_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1751,6 +1751,124 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>应用主Activity，管理底部导航栏和Fragment切换</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity:26]</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>继承AppCompatActivity，3个Tab页面的容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>onCreate</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Activity创建回调，初始化界面、边缘显示、底部导航和Fragment</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;onCreate:43]</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>设置EdgeToEdge，绑定底部导航选择监听器</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>switchFragment</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>fragmentClass&lt;Class&lt;T&gt;&gt;, fragmentRef&lt;Fragment&gt;, tag&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>通用Fragment切换方法，懒加载创建，隐藏/显示切换</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;switchFragment:122]</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>使用hide/show替代replace，避免重复创建Fragment实例</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/MainActivity_FunctionNameReg.xlsx
+++ b/ProjectDescription/MainActivity_FunctionNameReg.xlsx
@@ -437,17 +437,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="57" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="51" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1869,6 +1869,120 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>autoCheckUpdate</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>应用启动时自动检查更新，延迟3秒后调用，发现新版本弹窗提示</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>(app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;autoCheckUpdate:148]</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 13:52:08</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>showAutoUpdateDialog</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>updateManager&lt;UpdateManager&gt;, versionName&lt;String&gt;, releaseNotes&lt;String&gt;, apkUrl&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>显示自动发现的更新对话框，用户可选择立即更新或稍后</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>(app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;showAutoUpdateDialog:190]</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 13:52:08</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>startAutoDownload</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>updateManager&lt;UpdateManager&gt;, apkUrl&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>启动更新下载流程，显示进度对话框，下载完成后安装APK</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>(app/src/main/java/com/example/grayvideodl/MainActivity.java)[MainActivity-&gt;startAutoDownload:211]</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 13:52:08</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
